--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109590828</v>
+        <v>136384831</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>111302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,45 +961,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220240</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget no, Vstm</t>
+          <t>Digerberget, Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501763</v>
+        <v>501807</v>
       </c>
       <c r="R4" t="n">
-        <v>6594572</v>
+        <v>6594424</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,12 +1015,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med Linnea i området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1044,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1058,57 +1061,65 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109590828</t>
+          <t>https://artportalen.se/Sighting/136384831</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112704938</v>
+        <v>109590828</v>
       </c>
       <c r="B5" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Digerberget, Vstm</t>
+          <t>Digerberget no, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501734</v>
+        <v>501763</v>
       </c>
       <c r="R5" t="n">
-        <v>6594568</v>
+        <v>6594572</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,12 +1143,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,49 +1175,43 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112704938</t>
+          <t>https://artportalen.se/Sighting/109590828</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112997469</v>
+        <v>112704938</v>
       </c>
       <c r="B6" t="n">
-        <v>5179</v>
+        <v>93223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1214,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501775</v>
+        <v>501734</v>
       </c>
       <c r="R6" t="n">
-        <v>6594581</v>
+        <v>6594568</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,12 +1249,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,55 +1267,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # två torrgranar # Picea abies</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112997469</t>
+          <t>https://artportalen.se/Sighting/112704938</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112997472</v>
+        <v>136383564</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,46 +1298,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Vstm</t>
+          <t>Digerberget, Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501768</v>
+        <v>501717</v>
       </c>
       <c r="R7" t="n">
-        <v>6594555</v>
+        <v>6594593</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1381,12 +1357,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,48 +1381,296 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # en torrgran # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136383564</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112997469</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>501775</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6594581</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # två torrgranar # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112997469</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112997472</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>501768</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6594555</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # en torrgran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112997472</t>
         </is>
@@ -1450,6 +1684,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,10 +819,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112997447</v>
+        <v>136384084</v>
       </c>
       <c r="B3" t="n">
-        <v>58439</v>
+        <v>57990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,61 +830,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Digerberget, Vstm</t>
+          <t>Digerberget, Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501871</v>
+        <v>501752</v>
       </c>
       <c r="R3" t="n">
-        <v>6594416</v>
+        <v>6594472</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,12 +889,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i högstubbe gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,33 +923,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112997447</t>
+          <t>https://artportalen.se/Sighting/136384084</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136384831</v>
+        <v>112997447</v>
       </c>
       <c r="B4" t="n">
-        <v>111302</v>
+        <v>58439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,37 +977,61 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220240</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Vstm</t>
+          <t>Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501807</v>
+        <v>501871</v>
       </c>
       <c r="R4" t="n">
-        <v>6594424</v>
+        <v>6594416</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,27 +1055,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med Linnea i området</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,31 +1071,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136384831</t>
+          <t>https://artportalen.se/Sighting/112997447</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109590828</v>
+        <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>91872</v>
+        <v>111303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,45 +1108,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220240</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Digerberget no, Vstm</t>
+          <t>Digerberget, Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501763</v>
+        <v>501807</v>
       </c>
       <c r="R5" t="n">
-        <v>6594572</v>
+        <v>6594424</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1143,12 +1162,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med Linnea i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1191,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1175,57 +1208,65 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109590828</t>
+          <t>https://artportalen.se/Sighting/136384831</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112704938</v>
+        <v>109590828</v>
       </c>
       <c r="B6" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Digerberget, Vstm</t>
+          <t>Digerberget no, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501734</v>
+        <v>501763</v>
       </c>
       <c r="R6" t="n">
-        <v>6594568</v>
+        <v>6594572</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,12 +1290,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,59 +1322,57 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112704938</t>
+          <t>https://artportalen.se/Sighting/109590828</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136383564</v>
+        <v>112704938</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>93223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Vstm</t>
+          <t>Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501717</v>
+        <v>501734</v>
       </c>
       <c r="R7" t="n">
-        <v>6594593</v>
+        <v>6594568</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,22 +1396,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,6 +1410,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1398,16 +1428,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136383564</t>
+          <t>https://artportalen.se/Sighting/112704938</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112997469</v>
+        <v>136383564</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>57990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,46 +1445,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Digerberget, Vstm</t>
+          <t>Digerberget, Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501775</v>
+        <v>501717</v>
       </c>
       <c r="R8" t="n">
-        <v>6594581</v>
+        <v>6594593</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1478,12 +1504,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,59 +1528,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # två torrgranar # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112997469</t>
+          <t>https://artportalen.se/Sighting/136383564</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112997472</v>
+        <v>136383854</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>57990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,46 +1562,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Digerberget, Vstm</t>
+          <t>Digerberget, Digerberget, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501768</v>
+        <v>501682</v>
       </c>
       <c r="R9" t="n">
-        <v>6594555</v>
+        <v>6594523</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,12 +1621,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,13 +1650,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1655,22 +1675,296 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # en torrgran # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136383854</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112997469</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>501775</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6594581</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # två torrgranar # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112997469</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112997472</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Digerberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>501768</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6594555</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # en torrgran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112997472</t>
         </is>
@@ -1686,6 +1980,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -822,7 +822,7 @@
         <v>136384084</v>
       </c>
       <c r="B3" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>111303</v>
+        <v>111316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136383564</v>
       </c>
       <c r="B8" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136383854</v>
       </c>
       <c r="B9" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36452-2026 artfynd.xlsx
+++ b/artfynd/A 36452-2026 artfynd.xlsx
@@ -1100,7 +1100,7 @@
         <v>136384831</v>
       </c>
       <c r="B5" t="n">
-        <v>111316</v>
+        <v>111317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
